--- a/public/data/liste_bats.xlsx
+++ b/public/data/liste_bats.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="340">
   <si>
     <t xml:space="preserve">Code</t>
   </si>
@@ -760,10 +760,16 @@
     <t xml:space="preserve">I1</t>
   </si>
   <si>
+    <t xml:space="preserve">Partiel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zoologie - Aquarium Museum Centre Ville</t>
   </si>
   <si>
     <t xml:space="preserve">Quai Van Beneden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note : partiel. Étage 0</t>
   </si>
   <si>
     <t xml:space="preserve">L1</t>
@@ -1048,6 +1054,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1069,6 +1076,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1076,12 +1084,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1089,6 +1099,7 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1177,96 +1188,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1457,84 +1472,84 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="7.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="27.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="24.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="33.39"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="0" t="s">
+      <c r="I3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1542,28 +1557,28 @@
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="B4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="0" t="s">
+      <c r="I4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1571,28 +1586,28 @@
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="0" t="s">
+      <c r="I5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1600,28 +1615,28 @@
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="0" t="s">
+      <c r="I6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1629,28 +1644,28 @@
       <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="B7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="0" t="s">
+      <c r="I7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1658,28 +1673,28 @@
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="B8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="0" t="s">
+      <c r="I8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1687,28 +1702,28 @@
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="B9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1716,28 +1731,28 @@
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="0" t="s">
+      <c r="H10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="0" t="s">
+      <c r="I10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1745,45 +1760,45 @@
       <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="B11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="I11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="13"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="0" t="s">
+      <c r="B13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1791,28 +1806,28 @@
       <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H14" s="0" t="s">
+      <c r="G14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="0" t="s">
+      <c r="I14" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1820,28 +1835,28 @@
       <c r="A15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="0" t="s">
+      <c r="B15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="H15" s="0" t="s">
+      <c r="H15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J15" s="0" t="s">
+      <c r="J15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1849,28 +1864,28 @@
       <c r="A16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="0" t="s">
+      <c r="H16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="0" t="s">
+      <c r="I16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1878,28 +1893,28 @@
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="B17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="0" t="s">
+      <c r="H17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="0" t="s">
+      <c r="I17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1907,28 +1922,28 @@
       <c r="A18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="B18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="0" t="s">
+      <c r="G18" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="0" t="s">
+      <c r="I18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="0" t="s">
+      <c r="J18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1936,28 +1951,28 @@
       <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="B19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="0" t="s">
+      <c r="H19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J19" s="0" t="s">
+      <c r="J19" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1965,28 +1980,28 @@
       <c r="A20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="B20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H20" s="0" t="s">
+      <c r="H20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="0" t="s">
+      <c r="I20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1994,28 +2009,28 @@
       <c r="A21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="0" t="s">
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H21" s="0" t="s">
+      <c r="H21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="0" t="s">
+      <c r="I21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2023,25 +2038,25 @@
       <c r="A22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="B22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="0" t="s">
+      <c r="H22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="0" t="s">
+      <c r="I22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2049,28 +2064,28 @@
       <c r="A23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="0" t="s">
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="H23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="0" t="s">
+      <c r="I23" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2078,28 +2093,28 @@
       <c r="A24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="B24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H24" s="0" t="s">
+      <c r="H24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="0" t="s">
+      <c r="I24" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2107,28 +2122,28 @@
       <c r="A25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="B25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="0" t="s">
+      <c r="H25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="0" t="s">
+      <c r="I25" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2136,28 +2151,28 @@
       <c r="A26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="B26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="0" t="s">
+      <c r="H26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I26" s="0" t="s">
+      <c r="I26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J26" s="0" t="s">
+      <c r="J26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2165,28 +2180,28 @@
       <c r="A27" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="0" t="s">
+      <c r="B27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="H27" s="0" t="s">
+      <c r="H27" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="0" t="s">
+      <c r="I27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="0" t="s">
+      <c r="J27" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2194,28 +2209,28 @@
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="0" t="s">
+      <c r="B28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="0" t="s">
+      <c r="H28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I28" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="0" t="s">
+      <c r="I28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2223,25 +2238,25 @@
       <c r="A29" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="0" t="s">
+      <c r="B29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H29" s="0" t="s">
+      <c r="H29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I29" s="0" t="s">
+      <c r="I29" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J29" s="0" t="s">
+      <c r="J29" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2249,22 +2264,22 @@
       <c r="A30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="B30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I30" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30" s="0" t="s">
+      <c r="I30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2272,28 +2287,28 @@
       <c r="A31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="B31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H31" s="0" t="s">
+      <c r="G31" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="0" t="s">
+      <c r="I31" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J31" s="0" t="s">
+      <c r="J31" s="2" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2301,28 +2316,28 @@
       <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="0" t="s">
+      <c r="B32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G32" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H32" s="0" t="s">
+      <c r="H32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I32" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32" s="0" t="s">
+      <c r="I32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2330,28 +2345,28 @@
       <c r="A33" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="0" t="s">
+      <c r="B33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H33" s="0" t="s">
+      <c r="H33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I33" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="0" t="s">
+      <c r="I33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2359,28 +2374,28 @@
       <c r="A34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="0" t="s">
+      <c r="B34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="0" t="s">
+      <c r="H34" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I34" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="0" t="s">
+      <c r="I34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2388,28 +2403,28 @@
       <c r="A35" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="0" t="s">
+      <c r="B35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H35" s="0" t="s">
+      <c r="H35" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I35" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="0" t="s">
+      <c r="I35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2417,28 +2432,28 @@
       <c r="A36" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="0" t="s">
+      <c r="B36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H36" s="0" t="s">
+      <c r="G36" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I36" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="0" t="s">
+      <c r="I36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2446,28 +2461,28 @@
       <c r="A37" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="0" t="s">
+      <c r="B37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H37" s="0" t="s">
+      <c r="G37" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I37" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" s="0" t="s">
+      <c r="I37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2475,28 +2490,28 @@
       <c r="A38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="0" t="s">
+      <c r="B38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G38" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="0" t="s">
+      <c r="H38" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I38" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" s="0" t="s">
+      <c r="I38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2504,28 +2519,28 @@
       <c r="A39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="B39" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="0" t="s">
+      <c r="H39" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="0" t="s">
+      <c r="I39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J39" s="0" t="s">
+      <c r="J39" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2533,28 +2548,28 @@
       <c r="A40" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="B40" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G40" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H40" s="0" t="s">
+      <c r="H40" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J40" s="0" t="s">
+      <c r="J40" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2562,28 +2577,28 @@
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="0" t="s">
+      <c r="B41" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H41" s="0" t="s">
+      <c r="G41" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="0" t="s">
+      <c r="J41" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2591,28 +2606,28 @@
       <c r="A42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="0" t="s">
+      <c r="B42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="0" t="s">
+      <c r="H42" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I42" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="0" t="s">
+      <c r="I42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2620,28 +2635,28 @@
       <c r="A43" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="0" t="s">
+      <c r="B43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="0" t="s">
+      <c r="H43" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="I43" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" s="0" t="s">
+      <c r="I43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2649,28 +2664,28 @@
       <c r="A44" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="0" t="s">
+      <c r="B44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G44" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H44" s="0" t="s">
+      <c r="H44" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I44" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44" s="0" t="s">
+      <c r="I44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2678,28 +2693,28 @@
       <c r="A45" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="0" t="s">
+      <c r="B45" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="H45" s="0" t="s">
+      <c r="H45" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I45" s="0" t="s">
+      <c r="I45" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J45" s="0" t="s">
+      <c r="J45" s="2" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2707,28 +2722,28 @@
       <c r="A46" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C46" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="0" t="s">
+      <c r="C46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H46" s="0" t="s">
+      <c r="H46" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I46" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="0" t="s">
+      <c r="I46" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2736,28 +2751,28 @@
       <c r="A47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="0" t="s">
+      <c r="B47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="H47" s="0" t="s">
+      <c r="H47" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I47" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J47" s="0" t="s">
+      <c r="I47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2765,28 +2780,28 @@
       <c r="A48" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="0" t="s">
+      <c r="B48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H48" s="0" t="s">
+      <c r="H48" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J48" s="0" t="s">
+      <c r="I48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2794,28 +2809,28 @@
       <c r="A49" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="0" t="s">
+      <c r="B49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="0" t="s">
+      <c r="H49" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I49" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="0" t="s">
+      <c r="I49" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2823,28 +2838,28 @@
       <c r="A50" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="0" t="s">
+      <c r="B50" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H50" s="0" t="s">
+      <c r="H50" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J50" s="0" t="s">
+      <c r="J50" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2852,28 +2867,28 @@
       <c r="A51" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="0" t="s">
+      <c r="B51" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="0" t="s">
+      <c r="H51" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J51" s="0" t="s">
+      <c r="J51" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2881,28 +2896,28 @@
       <c r="A52" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="0" t="s">
+      <c r="B52" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G52" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H52" s="0" t="s">
+      <c r="H52" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I52" s="10" t="s">
+      <c r="I52" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="J52" s="0" t="s">
+      <c r="J52" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2910,154 +2925,154 @@
       <c r="A53" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="0" t="s">
+      <c r="B53" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H53" s="0" t="s">
+      <c r="H53" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I53" s="10" t="s">
+      <c r="I53" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="J53" s="0" t="s">
+      <c r="J53" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="54" s="19" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16" t="s">
+    <row r="54" s="20" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="B54" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="F54" s="17"/>
-      <c r="G54" s="18" t="n">
+      <c r="F54" s="18"/>
+      <c r="G54" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="0" t="s">
+      <c r="H54" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J54" s="17" t="s">
+      <c r="J54" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="17"/>
-      <c r="Y54" s="17"/>
-      <c r="Z54" s="17"/>
-      <c r="AA54" s="17"/>
-      <c r="AB54" s="17"/>
-      <c r="AC54" s="17"/>
-      <c r="XFD54" s="0"/>
-    </row>
-    <row r="55" s="20" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="18"/>
+      <c r="Z54" s="18"/>
+      <c r="AA54" s="18"/>
+      <c r="AB54" s="18"/>
+      <c r="AC54" s="18"/>
+      <c r="XFD54" s="2"/>
+    </row>
+    <row r="55" s="21" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="17" t="s">
+      <c r="B55" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F55" s="17"/>
-      <c r="G55" s="18" t="n">
+      <c r="F55" s="18"/>
+      <c r="G55" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="H55" s="17" t="s">
+      <c r="H55" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I55" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="J55" s="0" t="s">
+      <c r="J55" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-      <c r="R55" s="17"/>
-      <c r="S55" s="17"/>
-      <c r="T55" s="17"/>
-      <c r="U55" s="17"/>
-      <c r="V55" s="17"/>
-      <c r="W55" s="17"/>
-      <c r="X55" s="17"/>
-      <c r="Y55" s="17"/>
-      <c r="Z55" s="17"/>
-      <c r="AA55" s="17"/>
-      <c r="AB55" s="17"/>
-      <c r="AC55" s="17"/>
-      <c r="XFD55" s="0"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="18"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="18"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="18"/>
+      <c r="X55" s="18"/>
+      <c r="Y55" s="18"/>
+      <c r="Z55" s="18"/>
+      <c r="AA55" s="18"/>
+      <c r="AB55" s="18"/>
+      <c r="AC55" s="18"/>
+      <c r="XFD55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="0" t="s">
+      <c r="B56" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H56" s="0" t="s">
+      <c r="G56" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J56" s="0" t="s">
+      <c r="J56" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3065,28 +3080,28 @@
       <c r="A57" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="0" t="s">
+      <c r="B57" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H57" s="0" t="s">
+      <c r="H57" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="I57" s="0" t="s">
+      <c r="I57" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J57" s="0" t="s">
+      <c r="J57" s="2" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3094,28 +3109,28 @@
       <c r="A58" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B58" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="0" t="s">
+      <c r="B58" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G58" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H58" s="0" t="s">
+      <c r="H58" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I58" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J58" s="0" t="s">
+      <c r="I58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3123,28 +3138,28 @@
       <c r="A59" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="0" t="s">
+      <c r="B59" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="0" t="s">
+      <c r="H59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I59" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J59" s="0" t="s">
+      <c r="I59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3152,28 +3167,28 @@
       <c r="A60" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B60" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="0" t="s">
+      <c r="B60" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E60" s="0" t="s">
+      <c r="E60" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H60" s="0" t="s">
+      <c r="H60" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I60" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J60" s="0" t="s">
+      <c r="I60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3181,28 +3196,28 @@
       <c r="A61" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B61" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="0" t="s">
+      <c r="B61" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E61" s="0" t="s">
+      <c r="E61" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H61" s="0" t="s">
+      <c r="H61" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I61" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J61" s="0" t="s">
+      <c r="I61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J61" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3210,28 +3225,28 @@
       <c r="A62" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="0" t="s">
+      <c r="B62" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H62" s="0" t="s">
+      <c r="H62" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I62" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J62" s="0" t="s">
+      <c r="I62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J62" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3239,28 +3254,28 @@
       <c r="A63" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="0" t="s">
+      <c r="B63" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H63" s="0" t="s">
+      <c r="H63" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I63" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J63" s="0" t="s">
+      <c r="I63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J63" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3268,28 +3283,28 @@
       <c r="A64" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="0" t="s">
+      <c r="B64" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G64" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="0" t="s">
+      <c r="H64" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I64" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J64" s="0" t="s">
+      <c r="I64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J64" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3297,28 +3312,28 @@
       <c r="A65" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B65" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="0" t="s">
+      <c r="B65" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="0" t="s">
+      <c r="H65" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I65" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J65" s="0" t="s">
+      <c r="I65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3326,28 +3341,28 @@
       <c r="A66" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="0" t="s">
+      <c r="B66" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G66" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H66" s="0" t="s">
+      <c r="H66" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I66" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J66" s="0" t="s">
+      <c r="I66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J66" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3355,28 +3370,28 @@
       <c r="A67" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="0" t="s">
+      <c r="B67" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="H67" s="0" t="s">
+      <c r="H67" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I67" s="0" t="s">
+      <c r="I67" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J67" s="0" t="s">
+      <c r="J67" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3384,28 +3399,28 @@
       <c r="A68" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="0" t="s">
+      <c r="B68" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G68" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="H68" s="0" t="s">
+      <c r="H68" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I68" s="0" t="s">
+      <c r="I68" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J68" s="0" t="s">
+      <c r="J68" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3413,28 +3428,28 @@
       <c r="A69" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B69" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="0" t="s">
+      <c r="B69" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G69" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H69" s="0" t="s">
+      <c r="H69" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I69" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J69" s="0" t="s">
+      <c r="I69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J69" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3442,28 +3457,28 @@
       <c r="A70" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B70" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D70" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="0" t="s">
+      <c r="B70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G70" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H70" s="0" t="s">
+      <c r="H70" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I70" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J70" s="0" t="s">
+      <c r="I70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J70" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3471,28 +3486,28 @@
       <c r="A71" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="0" t="s">
+      <c r="B71" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G71" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="H71" s="0" t="s">
+      <c r="H71" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I71" s="0" t="s">
+      <c r="I71" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J71" s="0" t="s">
+      <c r="J71" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3500,25 +3515,25 @@
       <c r="A72" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="0" t="s">
+      <c r="B72" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H72" s="0" t="s">
+      <c r="H72" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I72" s="10" t="s">
+      <c r="I72" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="J72" s="0" t="s">
+      <c r="J72" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3526,25 +3541,25 @@
       <c r="A73" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="0" t="s">
+      <c r="B73" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H73" s="0" t="s">
+      <c r="H73" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I73" s="0" t="s">
+      <c r="I73" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J73" s="0" t="s">
+      <c r="J73" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3552,28 +3567,28 @@
       <c r="A74" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="0" t="s">
+      <c r="B74" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G74" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H74" s="0" t="s">
+      <c r="H74" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I74" s="0" t="s">
+      <c r="I74" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J74" s="0" t="s">
+      <c r="J74" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3581,28 +3596,28 @@
       <c r="A75" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B75" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="0" t="s">
+      <c r="B75" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G75" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H75" s="0" t="s">
+      <c r="H75" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I75" s="0" t="s">
+      <c r="I75" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J75" s="0" t="s">
+      <c r="J75" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3610,22 +3625,22 @@
       <c r="A76" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B76" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E76" s="0" t="s">
+      <c r="B76" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="I76" s="0" t="s">
+      <c r="I76" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J76" s="0" t="s">
+      <c r="J76" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3633,28 +3648,28 @@
       <c r="A77" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" s="0" t="s">
+      <c r="B77" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G77" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H77" s="0" t="s">
+      <c r="H77" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I77" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J77" s="0" t="s">
+      <c r="I77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J77" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3662,28 +3677,28 @@
       <c r="A78" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B78" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="0" t="s">
+      <c r="B78" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D78" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" s="0" t="s">
+      <c r="D78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H78" s="0" t="s">
+      <c r="H78" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I78" s="0" t="s">
+      <c r="I78" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J78" s="0" t="s">
+      <c r="J78" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3691,28 +3706,28 @@
       <c r="A79" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" s="0" t="s">
+      <c r="B79" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G79" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H79" s="0" t="s">
+      <c r="H79" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J79" s="0" t="s">
+      <c r="I79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J79" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3720,19 +3735,19 @@
       <c r="A80" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D80" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80" s="0" t="s">
+      <c r="B80" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="J80" s="0" t="s">
+      <c r="J80" s="2" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3740,28 +3755,28 @@
       <c r="A81" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E81" s="0" t="s">
+      <c r="B81" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G81" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="0" t="s">
+      <c r="H81" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I81" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J81" s="0" t="s">
+      <c r="I81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J81" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3769,28 +3784,28 @@
       <c r="A82" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E82" s="0" t="s">
+      <c r="B82" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G82" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H82" s="0" t="s">
+      <c r="H82" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I82" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J82" s="0" t="s">
+      <c r="I82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J82" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3798,28 +3813,28 @@
       <c r="A83" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B83" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C83" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E83" s="0" t="s">
+      <c r="B83" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G83" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H83" s="0" t="s">
+      <c r="H83" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I83" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J83" s="0" t="s">
+      <c r="I83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J83" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3827,898 +3842,904 @@
       <c r="A84" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E84" s="0" t="s">
+      <c r="B84" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="H84" s="0" t="s">
+      <c r="H84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I84" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J84" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="85" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12" t="s">
+      <c r="I84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="G85" s="13"/>
+      <c r="G85" s="14"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E86" s="0" t="s">
+      <c r="B86" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="G86" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H86" s="0" t="s">
+      <c r="H86" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="I86" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J86" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="87" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="12" t="s">
+      <c r="I86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="G87" s="13"/>
+      <c r="G87" s="14"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C88" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E88" s="0" t="s">
+      <c r="B88" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="G88" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="H88" s="0" t="s">
+      <c r="H88" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J88" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="89" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12" t="s">
+      <c r="J88" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="G89" s="13"/>
+      <c r="G89" s="14"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="91" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="12" t="s">
+    <row r="91" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="G91" s="13"/>
+      <c r="G91" s="14"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B92" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E92" s="0" t="s">
+      <c r="B92" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="C92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G92" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="H92" s="0" t="s">
-        <v>247</v>
-      </c>
-      <c r="I92" s="11" t="s">
+      <c r="H92" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I92" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J92" s="0" t="s">
-        <v>18</v>
+      <c r="J92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E93" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="G93" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G93" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H93" s="0" t="s">
-        <v>250</v>
-      </c>
-      <c r="I93" s="11" t="s">
+      <c r="H93" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I93" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J93" s="0" t="s">
+      <c r="J93" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="G94" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G94" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H94" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="I94" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J94" s="0" t="s">
-        <v>18</v>
+      <c r="H94" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I94" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C95" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E95" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H95" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="G95" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H95" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="I95" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J95" s="0" t="s">
+      <c r="I95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J95" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D96" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E96" s="0" t="s">
-        <v>257</v>
-      </c>
-      <c r="G96" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G96" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H96" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="I96" s="0" t="s">
+      <c r="H96" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I96" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J96" s="0" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="97" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="12" t="s">
+      <c r="J96" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G97" s="13"/>
+    </row>
+    <row r="97" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="G97" s="14"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D98" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E98" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="H98" s="0" t="s">
         <v>262</v>
       </c>
-      <c r="I98" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J98" s="0" t="s">
+      <c r="B98" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J98" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D99" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="0" t="s">
-        <v>264</v>
-      </c>
-      <c r="G99" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H99" s="0" t="s">
+      <c r="B99" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="I99" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J99" s="0" t="s">
+      <c r="G99" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J99" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G100" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B100" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C100" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D100" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E100" s="0" t="s">
+      <c r="H100" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H100" s="0" t="s">
-        <v>266</v>
-      </c>
-      <c r="I100" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J100" s="0" t="s">
+      <c r="I100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E101" s="0" t="s">
-        <v>270</v>
-      </c>
-      <c r="I101" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J101" s="0" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="102" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="12" t="s">
+      <c r="B101" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="G102" s="13"/>
+      <c r="I101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="G102" s="14"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C103" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D103" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E103" s="0" t="s">
-        <v>274</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H103" s="0" t="s">
         <v>275</v>
       </c>
-      <c r="I103" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J103" s="0" t="s">
+      <c r="B103" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J103" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E104" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="G104" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H104" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="I104" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J104" s="0" t="s">
+      <c r="I104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J104" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105" s="0" t="s">
-        <v>279</v>
-      </c>
-      <c r="G105" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G105" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="H105" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="I105" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J105" s="0" t="s">
+      <c r="H105" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J105" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D106" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E106" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="G106" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="H106" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="I106" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J106" s="0" t="s">
+      <c r="I106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J106" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D107" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E107" s="0" t="s">
-        <v>284</v>
-      </c>
-      <c r="G107" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G107" s="3" t="n">
         <v>203</v>
       </c>
-      <c r="H107" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="I107" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J107" s="0" t="s">
+      <c r="H107" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J107" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D108" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E108" s="0" t="s">
-        <v>286</v>
-      </c>
-      <c r="G108" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G108" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="H108" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="I108" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J108" s="0" t="s">
+      <c r="H108" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J108" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D109" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E109" s="0" t="s">
-        <v>288</v>
-      </c>
-      <c r="G109" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G109" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="H109" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="I109" s="0" t="s">
+      <c r="H109" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I109" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J109" s="0" t="s">
+      <c r="J109" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D110" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E110" s="0" t="s">
-        <v>290</v>
-      </c>
-      <c r="G110" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G110" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="H110" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="I110" s="0" t="s">
+      <c r="H110" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I110" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J110" s="0" t="s">
+      <c r="J110" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="111" s="21" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="G111" s="22"/>
+    <row r="111" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="G111" s="23"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D112" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E112" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="G112" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G112" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="H112" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="I112" s="0" t="s">
+      <c r="H112" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I112" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J112" s="0" t="s">
+      <c r="J112" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D113" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E113" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="H113" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="I113" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J113" s="0" t="s">
+      <c r="I113" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J113" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C114" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D114" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E114" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G114" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G114" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="H114" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="I114" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J114" s="0" t="s">
+      <c r="H114" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J114" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C115" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E115" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="H115" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="I115" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I115" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J115" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="116" s="21" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="G116" s="22"/>
+      <c r="J115" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="G116" s="23"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B117" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="118" s="21" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G118" s="22"/>
+    <row r="118" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="G118" s="23"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E119" s="0" t="s">
-        <v>306</v>
-      </c>
-      <c r="G119" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G119" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H119" s="0" t="s">
+      <c r="H119" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E120" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E121" s="0" t="s">
-        <v>310</v>
-      </c>
-      <c r="G121" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G121" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="H121" s="0" t="s">
-        <v>311</v>
+      <c r="H121" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E122" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="G122" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G122" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H122" s="0" t="s">
-        <v>314</v>
+      <c r="H122" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E123" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="G123" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G123" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H123" s="0" t="s">
-        <v>317</v>
+      <c r="H123" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E124" s="0" t="s">
-        <v>319</v>
-      </c>
-      <c r="H124" s="0" t="s">
         <v>320</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E125" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="H125" s="0" t="s">
         <v>323</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E126" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E127" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="G127" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="H127" s="0" t="s">
+      <c r="E127" s="2" t="s">
         <v>329</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E128" s="0" t="s">
-        <v>331</v>
-      </c>
-      <c r="G128" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G128" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="H128" s="0" t="s">
-        <v>332</v>
+      <c r="H128" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E130" s="0" t="s">
-        <v>333</v>
-      </c>
-      <c r="H130" s="0" t="s">
-        <v>334</v>
+      <c r="E130" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E131" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="H131" s="0" t="s">
+      <c r="E131" s="2" t="s">
         <v>337</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
